--- a/artfynd/A 54262-2025 artfynd.xlsx
+++ b/artfynd/A 54262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79126983</v>
+        <v>126017172</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flötutträsk, Nb</t>
+          <t>Strömnäs, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763245.6165241597</v>
+        <v>763359</v>
       </c>
       <c r="R2" t="n">
-        <v>7262860.737274689</v>
+        <v>7262861</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79126985</v>
+        <v>126017170</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +792,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flötutträsk, Nb</t>
+          <t>Strömnäs, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763190.2284376824</v>
+        <v>763262</v>
       </c>
       <c r="R3" t="n">
-        <v>7263060.682366084</v>
+        <v>7262597</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017170</v>
+        <v>79126995</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>79351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,41 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömnäs, Nb</t>
+          <t>Flötutträsk, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763262</v>
+        <v>763372</v>
       </c>
       <c r="R4" t="n">
-        <v>7262597</v>
+        <v>7262510</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,17 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,15 +972,302 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>79126984</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flötutträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>763151</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7263007</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>79126985</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flötutträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>763190</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7263061</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79126996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flötutträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>763313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7262380</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54262-2025 artfynd.xlsx
+++ b/artfynd/A 54262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017170</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79126995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79126984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79126985</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79126996</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>